--- a/public/bostads_data.xlsx
+++ b/public/bostads_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jona/Repos/moderate_website/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7268A49-D00C-684C-AB0F-9DB6DF8FD3B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F0E214D-3858-C746-9A3A-2175DFA6ADB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2680" yWindow="1600" windowWidth="28240" windowHeight="17240" xr2:uid="{7D5C1161-8802-4E42-AC66-A3E360909D2E}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <definedName name="_ftnref1" localSheetId="0">Tabelle1!$A$1</definedName>
     <definedName name="_ftnref2" localSheetId="0">Tabelle1!$E$1</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>Antal bostäder 2022</t>
   </si>
@@ -154,6 +154,9 @@
   </si>
   <si>
     <t>Antal flerbostadshus 2060 (hög)</t>
+  </si>
+  <si>
+    <t>Förtätning</t>
   </si>
 </sst>
 </file>
@@ -161,7 +164,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -254,34 +257,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -290,6 +293,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -625,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{474A4554-A23A-9A4B-945B-D57576865BE1}">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
@@ -639,9 +645,10 @@
     <col min="9" max="9" width="26.1640625" style="11" customWidth="1"/>
     <col min="10" max="10" width="22.1640625" customWidth="1"/>
     <col min="11" max="11" width="28.83203125" customWidth="1"/>
+    <col min="12" max="12" width="10.83203125" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>30</v>
       </c>
@@ -675,8 +682,11 @@
       <c r="K1" s="13" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L1" s="14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>4</v>
       </c>
@@ -715,8 +725,12 @@
         <f>D2+G2</f>
         <v>39861</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L2" s="11">
+        <f>G2/D2*100</f>
+        <v>74.362451336336989</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
@@ -755,8 +769,12 @@
         <f t="shared" ref="K3:K27" si="4">D3+G3</f>
         <v>10741</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L3" s="11">
+        <f t="shared" ref="L3:L27" si="5">G3/D3*100</f>
+        <v>77.801688462175136</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
         <v>6</v>
       </c>
@@ -795,8 +813,12 @@
         <f t="shared" si="4"/>
         <v>7052</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L4" s="11">
+        <f t="shared" si="5"/>
+        <v>385.67493112947659</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>7</v>
       </c>
@@ -835,8 +857,12 @@
         <f t="shared" si="4"/>
         <v>43491</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L5" s="11">
+        <f t="shared" si="5"/>
+        <v>91.666299413864522</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
         <v>8</v>
       </c>
@@ -875,8 +901,12 @@
         <f t="shared" si="4"/>
         <v>55878</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L6" s="11">
+        <f t="shared" si="5"/>
+        <v>135.99121547427993</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
@@ -915,8 +945,12 @@
         <f t="shared" si="4"/>
         <v>53218</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L7" s="11">
+        <f t="shared" si="5"/>
+        <v>114.43307276976388</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>10</v>
       </c>
@@ -955,8 +989,12 @@
         <f t="shared" si="4"/>
         <v>19245</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L8" s="11">
+        <f t="shared" si="5"/>
+        <v>41.040674239648226</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>11</v>
       </c>
@@ -995,8 +1033,12 @@
         <f t="shared" si="4"/>
         <v>54675</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L9" s="11">
+        <f t="shared" si="5"/>
+        <v>94.746215494211924</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>12</v>
       </c>
@@ -1035,8 +1077,12 @@
         <f t="shared" si="4"/>
         <v>29578</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L10" s="11">
+        <f t="shared" si="5"/>
+        <v>135.15662267451106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
         <v>13</v>
       </c>
@@ -1075,8 +1121,12 @@
         <f t="shared" si="4"/>
         <v>5274</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L11" s="11">
+        <f t="shared" si="5"/>
+        <v>257.80189959294432</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
         <v>14</v>
       </c>
@@ -1115,8 +1165,12 @@
         <f t="shared" si="4"/>
         <v>12884</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L12" s="11">
+        <f t="shared" si="5"/>
+        <v>76.880834706205377</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
         <v>15</v>
       </c>
@@ -1155,8 +1209,12 @@
         <f t="shared" si="4"/>
         <v>6597</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L13" s="11">
+        <f t="shared" si="5"/>
+        <v>135.85984983911334</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
         <v>16</v>
       </c>
@@ -1195,8 +1253,12 @@
         <f t="shared" si="4"/>
         <v>24180</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L14" s="11">
+        <f t="shared" si="5"/>
+        <v>89.201877934272304</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
         <v>17</v>
       </c>
@@ -1235,8 +1297,12 @@
         <f t="shared" si="4"/>
         <v>34110</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L15" s="11">
+        <f t="shared" si="5"/>
+        <v>99.357101110461727</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
         <v>18</v>
       </c>
@@ -1275,8 +1341,12 @@
         <f t="shared" si="4"/>
         <v>66569</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L16" s="11">
+        <f t="shared" si="5"/>
+        <v>65.722323184545289</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
         <v>19</v>
       </c>
@@ -1315,8 +1385,12 @@
         <f t="shared" si="4"/>
         <v>633708</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L17" s="11">
+        <f t="shared" si="5"/>
+        <v>48.999783686175661</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
         <v>20</v>
       </c>
@@ -1355,8 +1429,12 @@
         <f t="shared" si="4"/>
         <v>50451</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L18" s="11">
+        <f t="shared" si="5"/>
+        <v>111.52572219194164</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
         <v>21</v>
       </c>
@@ -1395,8 +1473,12 @@
         <f t="shared" si="4"/>
         <v>49487</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L19" s="11">
+        <f t="shared" si="5"/>
+        <v>72.506710356607513</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
         <v>22</v>
       </c>
@@ -1435,8 +1517,12 @@
         <f t="shared" si="4"/>
         <v>18934</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L20" s="11">
+        <f t="shared" si="5"/>
+        <v>81.464443166570817</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
         <v>23</v>
       </c>
@@ -1475,8 +1561,12 @@
         <f t="shared" si="4"/>
         <v>43490</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L21" s="11">
+        <f t="shared" si="5"/>
+        <v>157.48963883955003</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
         <v>24</v>
       </c>
@@ -1515,8 +1605,12 @@
         <f t="shared" si="4"/>
         <v>16166</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L22" s="11">
+        <f t="shared" si="5"/>
+        <v>110.87920688755544</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
         <v>25</v>
       </c>
@@ -1555,8 +1649,12 @@
         <f t="shared" si="4"/>
         <v>24152</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L23" s="11">
+        <f t="shared" si="5"/>
+        <v>74.357493502743282</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
         <v>26</v>
       </c>
@@ -1595,8 +1693,12 @@
         <f t="shared" si="4"/>
         <v>16137</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L24" s="11">
+        <f t="shared" si="5"/>
+        <v>240.65864471184292</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
         <v>27</v>
       </c>
@@ -1635,8 +1737,12 @@
         <f t="shared" si="4"/>
         <v>6049</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L25" s="11">
+        <f t="shared" si="5"/>
+        <v>168.96398399288572</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>28</v>
       </c>
@@ -1675,8 +1781,12 @@
         <f t="shared" si="4"/>
         <v>19714</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L26" s="11">
+        <f t="shared" si="5"/>
+        <v>202.64046668713542</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>29</v>
       </c>
@@ -1715,11 +1825,15 @@
         <f t="shared" si="4"/>
         <v>18607</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+      <c r="L27" s="11">
+        <f t="shared" si="5"/>
+        <v>244.12798224523766</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
     </row>
-    <row r="31" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
     </row>
   </sheetData>
